--- a/AAII_Financials/Quarterly/KHNGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KHNGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
   <si>
     <t>KHNGY</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,8 +1170,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1290,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1340,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1397,8 +1440,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +1590,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1890,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1961,60 +2040,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,55 +2137,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>763600</v>
+      </c>
+      <c r="E41" s="3">
         <v>933800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>945800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>756200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>730600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1008000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1271300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1096200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>959300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1992100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2388200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2150900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2268500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4360000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4085800</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2107,11 +2197,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>68100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2119,11 +2209,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>62900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2131,11 +2221,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>65300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2143,57 +2233,63 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6902200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6179900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6110100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6192800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6064500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5776300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5342200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5676500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5166900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5103900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4894000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4755700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5111400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5543400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6502900</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,8 +2335,11 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2286,196 +2385,211 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7988900</v>
+      </c>
+      <c r="E46" s="3">
         <v>7420300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7348500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7248700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7106900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7067100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6852900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7011900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6384400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7349900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7501800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7106700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7609000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10108300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10769200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E47" s="3">
         <v>32400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>36200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>34200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>35500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>34500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>40500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3680700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3798700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4130100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4062100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4067700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3735500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3185900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3318300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3143800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3130600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2726600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2510700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2484200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2461000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2332700</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3366300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3323700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3326800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3297000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3351000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3202700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2681600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2812800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2646300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2683900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2559200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2458200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2505400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2578300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2572800</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15279700</v>
+      </c>
+      <c r="E54" s="3">
         <v>14783300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15041300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14853600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14777200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14232700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12938900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13362000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12397100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13399500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13028800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12307400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12872400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15432500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15952700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +2877,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2638600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2378700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2552500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2484400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2535000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2440200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2336200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2577200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2402600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2350200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2389400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2156400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2335600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2410600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2953500</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1949300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1358900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1667200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1365700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1546600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1083800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>849700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>947100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1046100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>629700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>581900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>542400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>555400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>562100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>512600</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1878700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2008400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>697400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2932100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2797800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2857600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1572500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2761900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2686400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1904600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>862200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1985800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2608200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2698800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1518400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8195500</v>
+      </c>
+      <c r="E60" s="3">
         <v>7177200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7600700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8245800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8293900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7696100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7094600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7582500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7377000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6182600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6225200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6029600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7060300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7505900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8446300</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3105200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3156600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3323000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2706400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2736100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2017100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1739200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1775800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1680400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1877900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1577100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1477300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1425900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1409100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1325900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>941800</v>
+      </c>
+      <c r="E62" s="3">
         <v>866500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>866400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>797600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>817300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>813400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>82800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>82900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>71200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1034300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1049800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1014800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1022500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1332400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1317200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12704200</v>
+      </c>
+      <c r="E66" s="3">
         <v>11666600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12251700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12208700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12315200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10962200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9335900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9882700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9534800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9508300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9277200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8862900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9886500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10636400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11467900</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5238900</v>
+      </c>
+      <c r="E72" s="3">
         <v>5879400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5635900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5444100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5215800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5415500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5628000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5785400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5006700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5746900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5883200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5068400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4971700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6177800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5573900</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2534700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3076800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2749200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2603500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2415500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3268300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3600800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3471000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2854400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3884500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3744400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3436900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2978100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4788400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4477300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E83" s="3">
         <v>237600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>219600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>228500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>215900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>206200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>219700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>196800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>193900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>199000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>172200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>191600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>181300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>365100</v>
+      </c>
+      <c r="E89" s="3">
         <v>379000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>765500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>554300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>431300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>440100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>566100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>568200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>351700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>194000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>557000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>440700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>281600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>630100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1457800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-69000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-73900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-64500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-135400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-58000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-117900</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E94" s="3">
         <v>76000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-48900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-599600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-110100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-287100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-140100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-102700</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,55 +4612,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="D96" s="3">
+        <v>882400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>1231000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>1315400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>1856200</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,145 +4810,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-498800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-230600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-245900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-245800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1262400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-218300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-218500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-183500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1533500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-197300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-312300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-436300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2361300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-381300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-418500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-24900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-51100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-46900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-42200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-26300</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-143600</v>
+      </c>
+      <c r="E102" s="3">
         <v>225700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>430000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>245800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1007200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-386900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>302400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>249800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1243000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-259400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-63400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2166800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>208200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>894400</v>
       </c>
     </row>
